--- a/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
@@ -24706,13 +24706,13 @@
         <v>14</v>
       </c>
       <c r="BA111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB111" t="n">
         <v>4</v>
       </c>
       <c r="BC111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD111" t="n">
         <v>2.41</v>

--- a/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.25</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.18</v>
@@ -3966,7 +3966,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR16" t="n">
         <v>1.58</v>
@@ -4181,7 +4181,7 @@
         <v>2</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.42</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.08</v>
@@ -4838,7 +4838,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR20" t="n">
         <v>1.6</v>
@@ -5928,7 +5928,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR25" t="n">
         <v>0.93</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR28" t="n">
         <v>1.59</v>
@@ -7233,10 +7233,10 @@
         <v>3</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR31" t="n">
         <v>1.73</v>
@@ -8762,7 +8762,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR38" t="n">
         <v>1.81</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR40" t="n">
         <v>1.63</v>
@@ -9413,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.44</v>
@@ -10506,7 +10506,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR46" t="n">
         <v>1.59</v>
@@ -11375,7 +11375,7 @@
         <v>1.75</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.91</v>
@@ -12686,7 +12686,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR56" t="n">
         <v>1.49</v>
@@ -12904,7 +12904,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR57" t="n">
         <v>1.26</v>
@@ -13555,7 +13555,7 @@
         <v>0.25</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.18</v>
@@ -13773,7 +13773,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.9</v>
@@ -14866,7 +14866,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR66" t="n">
         <v>1.5</v>
@@ -15081,7 +15081,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.9</v>
@@ -15517,7 +15517,7 @@
         <v>1.83</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.64</v>
@@ -15956,7 +15956,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -17261,7 +17261,7 @@
         <v>1.57</v>
       </c>
       <c r="AP77" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.42</v>
@@ -17482,7 +17482,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR78" t="n">
         <v>1.34</v>
@@ -17918,7 +17918,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR80" t="n">
         <v>1.6</v>
@@ -18133,7 +18133,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.08</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.44</v>
@@ -19880,7 +19880,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR89" t="n">
         <v>1.51</v>
@@ -20095,7 +20095,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.64</v>
@@ -20752,7 +20752,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR93" t="n">
         <v>1.61</v>
@@ -20967,7 +20967,7 @@
         <v>1.67</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.25</v>
@@ -21188,7 +21188,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR95" t="n">
         <v>1.8</v>
@@ -21403,7 +21403,7 @@
         <v>0.22</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.18</v>
@@ -21621,10 +21621,10 @@
         <v>0.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR97" t="n">
         <v>1.85</v>
@@ -22714,7 +22714,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ102" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR102" t="n">
         <v>1.54</v>
@@ -23150,7 +23150,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR104" t="n">
         <v>2.08</v>
@@ -23583,7 +23583,7 @@
         <v>1.1</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.08</v>
@@ -23801,7 +23801,7 @@
         <v>1.55</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.42</v>
@@ -24688,22 +24688,22 @@
         <v>3.28</v>
       </c>
       <c r="AU111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW111" t="n">
         <v>2</v>
       </c>
       <c r="AX111" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA111" t="n">
         <v>2</v>
@@ -24906,19 +24906,19 @@
         <v>3.1</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV112" t="n">
         <v>2</v>
       </c>
       <c r="AW112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX112" t="n">
         <v>6</v>
       </c>
       <c r="AY112" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ112" t="n">
         <v>8</v>
@@ -24970,6 +24970,442 @@
       </c>
       <c r="BP112" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8218200</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F113" t="n">
+        <v>24</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Koper</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Mura</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>3</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>3</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>['30', '78', '90+4']</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>2</v>
+      </c>
+      <c r="R113" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U113" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V113" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W113" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X113" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>8218196</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>46082.5625</v>
+      </c>
+      <c r="F114" t="n">
+        <v>24</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T114" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U114" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V114" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X114" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
@@ -25124,7 +25124,7 @@
         <v>3.23</v>
       </c>
       <c r="AU113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV113" t="n">
         <v>2</v>
@@ -25136,7 +25136,7 @@
         <v>5</v>
       </c>
       <c r="AY113" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ113" t="n">
         <v>7</v>
@@ -25342,22 +25342,22 @@
         <v>3.55</v>
       </c>
       <c r="AU114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV114" t="n">
         <v>4</v>
       </c>
       <c r="AW114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY114" t="n">
         <v>9</v>
       </c>
-      <c r="AY114" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ114" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA114" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.64</v>
@@ -3966,7 +3966,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR16" t="n">
         <v>1.58</v>
@@ -5925,10 +5925,10 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR25" t="n">
         <v>0.93</v>
@@ -7236,7 +7236,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR31" t="n">
         <v>1.73</v>
@@ -7451,7 +7451,7 @@
         <v>2</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.91</v>
@@ -9198,7 +9198,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR40" t="n">
         <v>1.63</v>
@@ -9631,7 +9631,7 @@
         <v>2</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.9</v>
@@ -10506,7 +10506,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR46" t="n">
         <v>1.59</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.08</v>
@@ -12686,7 +12686,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR56" t="n">
         <v>1.49</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.38</v>
@@ -13991,7 +13991,7 @@
         <v>1.83</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.25</v>
@@ -14866,7 +14866,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR66" t="n">
         <v>1.5</v>
@@ -16607,7 +16607,7 @@
         <v>0.57</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.44</v>
@@ -17482,7 +17482,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR78" t="n">
         <v>1.34</v>
@@ -18351,7 +18351,7 @@
         <v>0.14</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.18</v>
@@ -21188,7 +21188,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR95" t="n">
         <v>1.8</v>
@@ -22057,7 +22057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.64</v>
@@ -22714,7 +22714,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR102" t="n">
         <v>1.54</v>
@@ -25330,7 +25330,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR114" t="n">
         <v>1.85</v>
@@ -25406,6 +25406,224 @@
       </c>
       <c r="BP114" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>8218283</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>46086.5625</v>
+      </c>
+      <c r="F115" t="n">
+        <v>23</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Aluminij</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Celje</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>['57', '90+2']</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U115" t="n">
+        <v>4</v>
+      </c>
+      <c r="V115" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR11" t="n">
         <v>1.53</v>
@@ -3309,7 +3309,7 @@
         <v>3</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.42</v>
@@ -5274,7 +5274,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR22" t="n">
         <v>1.31</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.44</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR34" t="n">
         <v>1.43</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.08</v>
@@ -10942,7 +10942,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR48" t="n">
         <v>1.22</v>
@@ -11593,7 +11593,7 @@
         <v>1.75</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.64</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.25</v>
@@ -13558,7 +13558,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR60" t="n">
         <v>1.74</v>
@@ -14430,7 +14430,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR64" t="n">
         <v>1.72</v>
@@ -14863,7 +14863,7 @@
         <v>2.71</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.77</v>
@@ -16171,7 +16171,7 @@
         <v>1.14</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.91</v>
@@ -16392,7 +16392,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR73" t="n">
         <v>1.66</v>
@@ -18354,7 +18354,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR82" t="n">
         <v>1.44</v>
@@ -18569,7 +18569,7 @@
         <v>1.63</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.9</v>
@@ -20316,7 +20316,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR91" t="n">
         <v>2.11</v>
@@ -21406,7 +21406,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR96" t="n">
         <v>1.89</v>
@@ -22493,7 +22493,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.42</v>
@@ -24240,7 +24240,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR109" t="n">
         <v>1.48</v>
@@ -25624,6 +25624,224 @@
       </c>
       <c r="BP115" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>8218204</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46088.5625</v>
+      </c>
+      <c r="F116" t="n">
+        <v>25</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Mura</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>NK Primorje</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>['25', '67', '71']</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U116" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V116" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X116" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Slovenia PrvaLiga_20252026.xlsx
@@ -25563,13 +25563,13 @@
         <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>5</v>
       </c>
       <c r="AX115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY115" t="n">
         <v>9</v>
